--- a/RobotOnTheFloor/RNN/Odometry.xlsx
+++ b/RobotOnTheFloor/RNN/Odometry.xlsx
@@ -491,22 +491,22 @@
         <v>24</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6155058354187191</v>
+        <v>0.7697148251061038</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03924047968571813</v>
+        <v>0.023502309162967</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2928575911573226</v>
+        <v>-0.1201684537142029</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1031114080855786</v>
+        <v>0.08933864591545856</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.522927303731731</v>
+        <v>0.01153645356490451</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7155184919847829</v>
+        <v>0.280334651371459</v>
       </c>
     </row>
     <row r="3">
@@ -525,22 +525,22 @@
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7084079951197757</v>
+        <v>0.806362317872466</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1743557000414351</v>
+        <v>0.0197621608644954</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.56925023106193</v>
+        <v>-0.5136117139568774</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2049096597033918</v>
+        <v>0.1207175764665701</v>
       </c>
       <c r="I3" t="n">
-        <v>-8.467590184364658</v>
+        <v>-1.898457710621901</v>
       </c>
       <c r="J3" t="n">
-        <v>2.685069776456331</v>
+        <v>0.8220213428735288</v>
       </c>
     </row>
     <row r="4">
@@ -559,22 +559,22 @@
         <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6185619632043501</v>
+        <v>0.8288746477385639</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03892857919063621</v>
+        <v>0.01746461072156715</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4775429339275179</v>
+        <v>-0.2141260922198409</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1178409234444634</v>
+        <v>0.096832204736612</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7110155323794032</v>
+        <v>0.3101318651663856</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4852550652885675</v>
+        <v>0.1956510624679457</v>
       </c>
     </row>
     <row r="5">
@@ -593,22 +593,22 @@
         <v>21</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8428715867303771</v>
+        <v>0.7736462109131432</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01603611934051168</v>
+        <v>0.0231010820986607</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.907238698638038</v>
+        <v>-1.322606563680773</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2318658125285938</v>
+        <v>0.1852386796874903</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3449110698466258</v>
+        <v>0.2932733478751206</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3814254731505428</v>
+        <v>0.2004322469481735</v>
       </c>
     </row>
     <row r="6">
@@ -627,22 +627,22 @@
         <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>-8.506462287566098</v>
+        <v>-12.54380660456951</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8920482068200498</v>
+        <v>1.270896368139595</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.727327801310708</v>
+        <v>-1.323748114486642</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1955988569328559</v>
+        <v>0.1219432524377476</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4652421347785149</v>
+        <v>0.1729512413595167</v>
       </c>
       <c r="J6" t="n">
-        <v>1.587338772454505</v>
+        <v>2.454955123954411</v>
       </c>
     </row>
     <row r="7">
@@ -661,22 +661,22 @@
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>-6.25991851940245</v>
+        <v>-2.605315561378548</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6812415703119253</v>
+        <v>0.3383083195685368</v>
       </c>
       <c r="G7" t="n">
-        <v>-29.7326173253117</v>
+        <v>-37.74650522785394</v>
       </c>
       <c r="H7" t="n">
-        <v>1.612754536177903</v>
+        <v>2.033299064827648</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.88425631911472</v>
+        <v>-1.254032914627871</v>
       </c>
       <c r="J7" t="n">
-        <v>11.52976152099894</v>
+        <v>6.690717561106953</v>
       </c>
     </row>
     <row r="8">
@@ -695,22 +695,22 @@
         <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.338524647928629</v>
+        <v>-11.52258163419275</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5009456930658718</v>
+        <v>1.175068722057629</v>
       </c>
       <c r="G8" t="n">
-        <v>-35.03365535585581</v>
+        <v>-16.27993316040618</v>
       </c>
       <c r="H8" t="n">
-        <v>1.890936932415606</v>
+        <v>0.9067984771457593</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6052117085358282</v>
+        <v>-0.3717564082723155</v>
       </c>
       <c r="J8" t="n">
-        <v>4.764800947624264</v>
+        <v>4.071828157799473</v>
       </c>
     </row>
     <row r="9">
@@ -729,22 +729,22 @@
         <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.690585483749319</v>
+        <v>-14.02516452742698</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7216536270435593</v>
+        <v>1.409901040831776</v>
       </c>
       <c r="G9" t="n">
-        <v>-49.96433778143706</v>
+        <v>-20.12597434026679</v>
       </c>
       <c r="H9" t="n">
-        <v>2.674453856965203</v>
+        <v>1.108627052092371</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8230998651479806</v>
+        <v>-0.4873883147639602</v>
       </c>
       <c r="J9" t="n">
-        <v>5.411565290035311</v>
+        <v>4.415062022028848</v>
       </c>
     </row>
     <row r="10">
@@ -763,22 +763,22 @@
         <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7791574665505888</v>
+        <v>-1.13728282138071</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01773294300407577</v>
+        <v>0.1716169157415334</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8285739529948599</v>
+        <v>-0.1237491177279815</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1083300121198298</v>
+        <v>0.06657414940409713</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.107389111889546</v>
+        <v>0.2086288482183044</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8477326696952049</v>
+        <v>0.3183423390747917</v>
       </c>
     </row>
     <row r="11">
@@ -797,22 +797,22 @@
         <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9280299861964942</v>
+        <v>-0.8228832902941148</v>
       </c>
       <c r="F11" t="n">
-        <v>0.005778959935145212</v>
+        <v>0.1463716476394816</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2624594822441314</v>
+        <v>0.6207022672889873</v>
       </c>
       <c r="H11" t="n">
-        <v>0.043694034412172</v>
+        <v>0.02247069521815697</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1576475617904889</v>
+        <v>0.6569647855575265</v>
       </c>
       <c r="J11" t="n">
-        <v>0.338850417912305</v>
+        <v>0.1379916772361245</v>
       </c>
     </row>
     <row r="12">
@@ -831,22 +831,22 @@
         <v>22</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2891717036509941</v>
+        <v>0.2655739781491577</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05707721908437836</v>
+        <v>0.05897204031656526</v>
       </c>
       <c r="G12" t="n">
-        <v>0.432525515084666</v>
+        <v>0.6820677210573657</v>
       </c>
       <c r="H12" t="n">
-        <v>0.03361883052522356</v>
+        <v>0.01883522817041762</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6994188318546275</v>
+        <v>0.7571642607847293</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6836197715602217</v>
+        <v>0.09768475519824156</v>
       </c>
     </row>
     <row r="13">
@@ -865,22 +865,22 @@
         <v>21</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6526413430029783</v>
+        <v>-0.2440410484527795</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02789177958742944</v>
+        <v>0.09989248294870352</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.201639955894025</v>
+        <v>-0.5309346638547368</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2489173088130717</v>
+        <v>0.09069699938491763</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.372199781133526</v>
+        <v>0.2594247384648035</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9542572096273156</v>
+        <v>0.2979088389654553</v>
       </c>
     </row>
     <row r="14">
@@ -899,22 +899,22 @@
         <v>24</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8346753865695842</v>
+        <v>0.5208559295798599</v>
       </c>
       <c r="F14" t="n">
-        <v>0.171698458281143</v>
+        <v>0.04484079243005055</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0389222992404602</v>
+        <v>0.4596086486847554</v>
       </c>
       <c r="H14" t="n">
-        <v>0.07109687030946009</v>
+        <v>0.03997609536715959</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.794627888911285</v>
+        <v>-0.01625709251409679</v>
       </c>
       <c r="J14" t="n">
-        <v>1.269437000762763</v>
+        <v>0.3399738770947356</v>
       </c>
     </row>
     <row r="15">
@@ -933,22 +933,22 @@
         <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.9315053614995246</v>
+        <v>0.5293997635881726</v>
       </c>
       <c r="F15" t="n">
-        <v>0.180760310602582</v>
+        <v>0.04404121603753124</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2552828633124586</v>
+        <v>0.3251383129711802</v>
       </c>
       <c r="H15" t="n">
-        <v>0.09286104845017415</v>
+        <v>0.04992369899082291</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.177664910113774</v>
+        <v>-0.4225016117242859</v>
       </c>
       <c r="J15" t="n">
-        <v>1.732111713418943</v>
+        <v>0.4758770115099663</v>
       </c>
     </row>
     <row r="16">
@@ -967,22 +967,22 @@
         <v>22</v>
       </c>
       <c r="E16" t="n">
-        <v>-5.07254910481107</v>
+        <v>0.7219441152112359</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5683007069071241</v>
+        <v>0.02602191487590396</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.020743385488753</v>
+        <v>0.01179751900427883</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1494869044336914</v>
+        <v>0.0731034583107219</v>
       </c>
       <c r="I16" t="n">
-        <v>-9.071511627085835</v>
+        <v>-1.337743513548745</v>
       </c>
       <c r="J16" t="n">
-        <v>3.36927622083738</v>
+        <v>0.7820577409089148</v>
       </c>
     </row>
     <row r="17">
@@ -1001,22 +1001,22 @@
         <v>21</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3588786003358746</v>
+        <v>0.6552566668260886</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1271709221025504</v>
+        <v>0.03226287289946047</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3852035639402303</v>
+        <v>0.3872390789450471</v>
       </c>
       <c r="H17" t="n">
-        <v>0.102472087386721</v>
+        <v>0.04532972068805631</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.848071717511081</v>
+        <v>-0.06303471094183921</v>
       </c>
       <c r="J17" t="n">
-        <v>1.287315848300162</v>
+        <v>0.3556226419744918</v>
       </c>
     </row>
   </sheetData>
